--- a/test-data/test2-clean.xlsx
+++ b/test-data/test2-clean.xlsx
@@ -397,7 +397,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:O21"/>
+  <dimension ref="A1:O22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -434,26 +434,26 @@
     </row>
     <row r="7">
       <c r="A7" t="str">
-        <v>FECHA DE ENTRADA</v>
+        <v>FECHA DE CONTRATO</v>
       </c>
       <c r="B7" t="str">
-        <v>10/06/2024</v>
+        <v>25/05/2024</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="str">
-        <v>FECHA DE SALIDA</v>
+        <v>FECHA DE ENTRADA</v>
       </c>
       <c r="B8" t="str">
-        <v>17/06/2024</v>
+        <v>10/06/2024</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="str">
-        <v>HORA</v>
+        <v>FECHA DE SALIDA</v>
       </c>
       <c r="B9" t="str">
-        <v>15:00</v>
+        <v>17/06/2024</v>
       </c>
     </row>
     <row r="10">
@@ -461,155 +461,116 @@
         <v>HORA</v>
       </c>
       <c r="B10" t="str">
-        <v>11:00</v>
+        <v>15:00</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="str">
-        <v>NUMERO DE PERSONAS</v>
+        <v>HORA</v>
       </c>
       <c r="B11" t="str">
-        <v>8</v>
+        <v>11:00</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="str">
-        <v>TIPO DE PAGO</v>
+        <v>NUMERO DE PERSONAS</v>
       </c>
       <c r="B12" t="str">
-        <v>TARJETA</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="str">
-        <v>Nombre</v>
+        <v>TIPO DE PAGO</v>
       </c>
       <c r="B13" t="str">
-        <v>1. Apellido</v>
-      </c>
-      <c r="C13" t="str">
-        <v>2. Apellido</v>
-      </c>
-      <c r="D13" t="str">
-        <v>Fecha de nacimiento</v>
-      </c>
-      <c r="E13" t="str">
-        <v>Nationality</v>
-      </c>
-      <c r="F13" t="str">
-        <v>Tipo de documento de identidad</v>
-      </c>
-      <c r="G13" t="str">
-        <v>Número de documento</v>
-      </c>
-      <c r="H13" t="str">
-        <v>Soporte de documento</v>
-      </c>
-      <c r="I13" t="str">
-        <v>Dirección de residencia</v>
-      </c>
-      <c r="J13" t="str">
-        <v>Código municipio</v>
-      </c>
-      <c r="K13" t="str">
-        <v>Correo electrónico</v>
-      </c>
-      <c r="L13" t="str">
-        <v>Número de teléfono</v>
-      </c>
-      <c r="M13" t="str">
-        <v>Fecha de llegada</v>
-      </c>
-      <c r="N13" t="str">
-        <v>Fecha de salida</v>
-      </c>
-      <c r="O13" t="str">
-        <v>Parentesco</v>
+        <v>TARJETA</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="str">
-        <v>Claire</v>
+        <v>Nombre</v>
       </c>
       <c r="B14" t="str">
-        <v>Lefebvre</v>
+        <v>1. Apellido</v>
       </c>
       <c r="C14" t="str">
-        <v>Moreau</v>
+        <v>2. Apellido</v>
       </c>
       <c r="D14" t="str">
-        <v>12/01/1987</v>
+        <v>Fecha de nacimiento</v>
       </c>
       <c r="E14" t="str">
-        <v>FRA</v>
+        <v>Nationality</v>
       </c>
       <c r="F14" t="str">
-        <v>PAS</v>
+        <v>Tipo de documento de identidad</v>
       </c>
       <c r="G14" t="str">
-        <v>06AB12345</v>
+        <v>Número de documento</v>
       </c>
       <c r="H14" t="str">
-        <v/>
+        <v>Soporte de documento</v>
       </c>
       <c r="I14" t="str">
-        <v>15 Avenue des Champs-Elysées, Paris, 75009</v>
+        <v>Dirección de residencia</v>
       </c>
       <c r="J14" t="str">
-        <v/>
+        <v>Código municipio</v>
       </c>
       <c r="K14" t="str">
-        <v>claire@example.com</v>
+        <v>Correo electrónico</v>
       </c>
       <c r="L14" t="str">
-        <v>+33612345678</v>
+        <v>Número de teléfono</v>
       </c>
       <c r="M14" t="str">
-        <v>10/06/2024</v>
+        <v>Fecha de llegada</v>
       </c>
       <c r="N14" t="str">
-        <v>17/06/2024</v>
+        <v>Fecha de salida</v>
       </c>
       <c r="O14" t="str">
-        <v>OT</v>
+        <v>Parentesco</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="str">
-        <v>Friedrich</v>
+        <v>Claire</v>
       </c>
       <c r="B15" t="str">
-        <v>Weber</v>
+        <v>Lefebvre</v>
       </c>
       <c r="C15" t="str">
-        <v/>
+        <v>Moreau</v>
       </c>
       <c r="D15" t="str">
-        <v>25/06/1970</v>
+        <v>12/01/1987</v>
       </c>
       <c r="E15" t="str">
-        <v>DEU</v>
+        <v>FRA</v>
       </c>
       <c r="F15" t="str">
         <v>PAS</v>
       </c>
       <c r="G15" t="str">
-        <v>L01X00T47</v>
+        <v>06AB12345</v>
       </c>
       <c r="H15" t="str">
         <v/>
       </c>
       <c r="I15" t="str">
-        <v>Kaiserstraße 12, Frankfurt, 60311</v>
+        <v>15 Avenue des Champs-Elysées, Paris, 75009</v>
       </c>
       <c r="J15" t="str">
         <v/>
       </c>
       <c r="K15" t="str">
-        <v>fweber@example.com</v>
+        <v>claire@example.com</v>
       </c>
       <c r="L15" t="str">
-        <v>+49176543210</v>
+        <v>+33612345678</v>
       </c>
       <c r="M15" t="str">
         <v>10/06/2024</v>
@@ -623,40 +584,40 @@
     </row>
     <row r="16">
       <c r="A16" t="str">
-        <v>Marco</v>
+        <v>Friedrich</v>
       </c>
       <c r="B16" t="str">
-        <v>Bianchi</v>
+        <v>Weber</v>
       </c>
       <c r="C16" t="str">
-        <v>Conti</v>
+        <v/>
       </c>
       <c r="D16" t="str">
-        <v>03/08/1993</v>
+        <v>25/06/1970</v>
       </c>
       <c r="E16" t="str">
-        <v>ITA</v>
+        <v>DEU</v>
       </c>
       <c r="F16" t="str">
         <v>PAS</v>
       </c>
       <c r="G16" t="str">
-        <v>YA1234567</v>
+        <v>L01X00T47</v>
       </c>
       <c r="H16" t="str">
         <v/>
       </c>
       <c r="I16" t="str">
-        <v>Corso Buenos Aires 10, Milano, 20124</v>
+        <v>Kaiserstraße 12, Frankfurt, 60311</v>
       </c>
       <c r="J16" t="str">
         <v/>
       </c>
       <c r="K16" t="str">
-        <v>marco@example.com</v>
+        <v>fweber@example.com</v>
       </c>
       <c r="L16" t="str">
-        <v>+39340987654</v>
+        <v>+49176543210</v>
       </c>
       <c r="M16" t="str">
         <v>10/06/2024</v>
@@ -670,40 +631,40 @@
     </row>
     <row r="17">
       <c r="A17" t="str">
-        <v>João</v>
+        <v>Marco</v>
       </c>
       <c r="B17" t="str">
-        <v>Silva</v>
+        <v>Bianchi</v>
       </c>
       <c r="C17" t="str">
-        <v>Costa</v>
+        <v>Conti</v>
       </c>
       <c r="D17" t="str">
-        <v>17/03/1985</v>
+        <v>03/08/1993</v>
       </c>
       <c r="E17" t="str">
-        <v>PRT</v>
+        <v>ITA</v>
       </c>
       <c r="F17" t="str">
         <v>PAS</v>
       </c>
       <c r="G17" t="str">
-        <v>AB123456</v>
+        <v>YA1234567</v>
       </c>
       <c r="H17" t="str">
         <v/>
       </c>
       <c r="I17" t="str">
-        <v>Rua Augusta 45, Lisboa, 1100-048</v>
+        <v>Corso Buenos Aires 10, Milano, 20124</v>
       </c>
       <c r="J17" t="str">
         <v/>
       </c>
       <c r="K17" t="str">
-        <v>joao@example.com</v>
+        <v>marco@example.com</v>
       </c>
       <c r="L17" t="str">
-        <v>+351912345678</v>
+        <v>+39340987654</v>
       </c>
       <c r="M17" t="str">
         <v>10/06/2024</v>
@@ -717,40 +678,40 @@
     </row>
     <row r="18">
       <c r="A18" t="str">
-        <v>Sophie</v>
+        <v>João</v>
       </c>
       <c r="B18" t="str">
-        <v>van den Berg</v>
+        <v>Silva</v>
       </c>
       <c r="C18" t="str">
-        <v/>
+        <v>Costa</v>
       </c>
       <c r="D18" t="str">
-        <v>29/11/1991</v>
+        <v>17/03/1985</v>
       </c>
       <c r="E18" t="str">
-        <v>NLD</v>
+        <v>PRT</v>
       </c>
       <c r="F18" t="str">
         <v>PAS</v>
       </c>
       <c r="G18" t="str">
-        <v>NX4567890</v>
+        <v>AB123456</v>
       </c>
       <c r="H18" t="str">
         <v/>
       </c>
       <c r="I18" t="str">
-        <v>Herengracht 400, Amsterdam, 1016 BW</v>
+        <v>Rua Augusta 45, Lisboa, 1100-048</v>
       </c>
       <c r="J18" t="str">
         <v/>
       </c>
       <c r="K18" t="str">
-        <v>sophie@example.com</v>
+        <v>joao@example.com</v>
       </c>
       <c r="L18" t="str">
-        <v>+31612345678</v>
+        <v>+351912345678</v>
       </c>
       <c r="M18" t="str">
         <v>10/06/2024</v>
@@ -764,40 +725,40 @@
     </row>
     <row r="19">
       <c r="A19" t="str">
-        <v>Thomas</v>
+        <v>Sophie</v>
       </c>
       <c r="B19" t="str">
-        <v>Dubois</v>
+        <v>van den Berg</v>
       </c>
       <c r="C19" t="str">
-        <v>Lambert</v>
+        <v/>
       </c>
       <c r="D19" t="str">
-        <v>14/05/1980</v>
+        <v>29/11/1991</v>
       </c>
       <c r="E19" t="str">
-        <v>BEL</v>
+        <v>NLD</v>
       </c>
       <c r="F19" t="str">
-        <v>OTRO</v>
+        <v>PAS</v>
       </c>
       <c r="G19" t="str">
-        <v>590-1234567-29</v>
+        <v>NX4567890</v>
       </c>
       <c r="H19" t="str">
         <v/>
       </c>
       <c r="I19" t="str">
-        <v>Rue Neuve 12, Bruxelles, 1000</v>
+        <v>Herengracht 400, Amsterdam, 1016 BW</v>
       </c>
       <c r="J19" t="str">
         <v/>
       </c>
       <c r="K19" t="str">
-        <v>thomas@example.com</v>
+        <v>sophie@example.com</v>
       </c>
       <c r="L19" t="str">
-        <v>+32470123456</v>
+        <v>+31612345678</v>
       </c>
       <c r="M19" t="str">
         <v>10/06/2024</v>
@@ -811,40 +772,40 @@
     </row>
     <row r="20">
       <c r="A20" t="str">
-        <v>Erik</v>
+        <v>Thomas</v>
       </c>
       <c r="B20" t="str">
-        <v>Johansson</v>
+        <v>Dubois</v>
       </c>
       <c r="C20" t="str">
-        <v/>
+        <v>Lambert</v>
       </c>
       <c r="D20" t="str">
-        <v>07/07/1995</v>
+        <v>14/05/1980</v>
       </c>
       <c r="E20" t="str">
-        <v>SWE</v>
+        <v>BEL</v>
       </c>
       <c r="F20" t="str">
-        <v>PAS</v>
+        <v>OTRO</v>
       </c>
       <c r="G20" t="str">
-        <v>XY1234567</v>
+        <v>590-1234567-29</v>
       </c>
       <c r="H20" t="str">
         <v/>
       </c>
       <c r="I20" t="str">
-        <v>Drottninggatan 10, Stockholm, 111 51</v>
+        <v>Rue Neuve 12, Bruxelles, 1000</v>
       </c>
       <c r="J20" t="str">
         <v/>
       </c>
       <c r="K20" t="str">
-        <v>erik@example.com</v>
+        <v>thomas@example.com</v>
       </c>
       <c r="L20" t="str">
-        <v>+46701234567</v>
+        <v>+32470123456</v>
       </c>
       <c r="M20" t="str">
         <v>10/06/2024</v>
@@ -858,40 +819,40 @@
     </row>
     <row r="21">
       <c r="A21" t="str">
-        <v>Nikos</v>
+        <v>Erik</v>
       </c>
       <c r="B21" t="str">
-        <v>Papadopoulos</v>
+        <v>Johansson</v>
       </c>
       <c r="C21" t="str">
-        <v>Alexiou</v>
+        <v/>
       </c>
       <c r="D21" t="str">
-        <v>21/09/1983</v>
+        <v>07/07/1995</v>
       </c>
       <c r="E21" t="str">
-        <v>GRC</v>
+        <v>SWE</v>
       </c>
       <c r="F21" t="str">
         <v>PAS</v>
       </c>
       <c r="G21" t="str">
-        <v>AE1234567</v>
+        <v>XY1234567</v>
       </c>
       <c r="H21" t="str">
         <v/>
       </c>
       <c r="I21" t="str">
-        <v>Ermou 15, Athina, 10563</v>
+        <v>Drottninggatan 10, Stockholm, 111 51</v>
       </c>
       <c r="J21" t="str">
         <v/>
       </c>
       <c r="K21" t="str">
-        <v>nikos@example.com</v>
+        <v>erik@example.com</v>
       </c>
       <c r="L21" t="str">
-        <v>+30691234567</v>
+        <v>+46701234567</v>
       </c>
       <c r="M21" t="str">
         <v>10/06/2024</v>
@@ -903,9 +864,56 @@
         <v>OT</v>
       </c>
     </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>Nikos</v>
+      </c>
+      <c r="B22" t="str">
+        <v>Papadopoulos</v>
+      </c>
+      <c r="C22" t="str">
+        <v>Alexiou</v>
+      </c>
+      <c r="D22" t="str">
+        <v>21/09/1983</v>
+      </c>
+      <c r="E22" t="str">
+        <v>GRC</v>
+      </c>
+      <c r="F22" t="str">
+        <v>PAS</v>
+      </c>
+      <c r="G22" t="str">
+        <v>AE1234567</v>
+      </c>
+      <c r="H22" t="str">
+        <v/>
+      </c>
+      <c r="I22" t="str">
+        <v>Ermou 15, Athina, 10563</v>
+      </c>
+      <c r="J22" t="str">
+        <v/>
+      </c>
+      <c r="K22" t="str">
+        <v>nikos@example.com</v>
+      </c>
+      <c r="L22" t="str">
+        <v>+30691234567</v>
+      </c>
+      <c r="M22" t="str">
+        <v>10/06/2024</v>
+      </c>
+      <c r="N22" t="str">
+        <v>17/06/2024</v>
+      </c>
+      <c r="O22" t="str">
+        <v>OT</v>
+      </c>
+    </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:O21"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:O22"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/test-data/test2-clean.xlsx
+++ b/test-data/test2-clean.xlsx
@@ -121,10 +121,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -156,10 +156,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
-        <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="宋体"/>
-        <a:font script="Hant" typeface="新細明體"/>
+        <a:font script="Jpan" typeface="ï¼­ï¼³ ï¼°ã´ã·ãã¯"/>
+        <a:font script="Hang" typeface="ë§ì ê³ ë"/>
+        <a:font script="Hans" typeface="å®ä½"/>
+        <a:font script="Hant" typeface="æ°ç´°æé«"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -401,7 +401,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>CODIGO 12345</v>
+        <v>CODIGO 0000004630</v>
       </c>
     </row>
     <row r="2">
